--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3271,6 +3271,729 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122467142</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92082</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>566070</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6522054</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122467759</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90773</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>565945</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6522131</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122471527</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80608</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>566071</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6522065</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122467685</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56589</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>565996</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6522087</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122466836</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79269</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>566112</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6521987</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122466971</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79269</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>566063</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6522107</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122467101</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79269</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>566070</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6522077</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122467142</v>
+        <v>122467101</v>
       </c>
       <c r="B25" t="n">
-        <v>92082</v>
+        <v>79269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,25 +3285,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
         <v>566070</v>
       </c>
       <c r="R25" t="n">
-        <v>6522054</v>
+        <v>6522077</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122467759</v>
+        <v>122466971</v>
       </c>
       <c r="B26" t="n">
-        <v>90773</v>
+        <v>79269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,25 +3387,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565945</v>
+        <v>566063</v>
       </c>
       <c r="R26" t="n">
-        <v>6522131</v>
+        <v>6522107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122471527</v>
+        <v>122467142</v>
       </c>
       <c r="B27" t="n">
-        <v>80608</v>
+        <v>92082</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3489,44 +3489,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566071</v>
+        <v>566070</v>
       </c>
       <c r="R27" t="n">
-        <v>6522065</v>
+        <v>6522054</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3564,7 +3561,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3583,10 +3579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467685</v>
+        <v>122466836</v>
       </c>
       <c r="B28" t="n">
-        <v>56589</v>
+        <v>79269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,43 +3591,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565996</v>
+        <v>566112</v>
       </c>
       <c r="R28" t="n">
-        <v>6522087</v>
+        <v>6521987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3690,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122466836</v>
+        <v>122467685</v>
       </c>
       <c r="B29" t="n">
-        <v>79269</v>
+        <v>56589</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3702,38 +3693,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566112</v>
+        <v>565996</v>
       </c>
       <c r="R29" t="n">
-        <v>6521987</v>
+        <v>6522087</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122466971</v>
+        <v>122471527</v>
       </c>
       <c r="B30" t="n">
-        <v>79269</v>
+        <v>80608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3808,37 +3804,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566063</v>
+        <v>566071</v>
       </c>
       <c r="R30" t="n">
-        <v>6522107</v>
+        <v>6522065</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3876,6 +3875,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467101</v>
+        <v>122467759</v>
       </c>
       <c r="B31" t="n">
-        <v>79269</v>
+        <v>90773</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3906,25 +3906,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R31" t="n">
-        <v>6522077</v>
+        <v>6522131</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3276,7 +3276,7 @@
         <v>122467101</v>
       </c>
       <c r="B25" t="n">
-        <v>79269</v>
+        <v>79270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3290,11 +3290,6 @@
       </c>
       <c r="E25" t="n">
         <v>6453</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3378,7 +3373,7 @@
         <v>122466971</v>
       </c>
       <c r="B26" t="n">
-        <v>79269</v>
+        <v>79270</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,11 +3387,6 @@
       </c>
       <c r="E26" t="n">
         <v>6453</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3477,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467142</v>
+        <v>122467759</v>
       </c>
       <c r="B27" t="n">
-        <v>92082</v>
+        <v>90778</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3493,21 +3483,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3517,10 +3502,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R27" t="n">
-        <v>6522054</v>
+        <v>6522131</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3579,10 +3564,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122466836</v>
+        <v>122467685</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>56589</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,38 +3576,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566112</v>
+        <v>565996</v>
       </c>
       <c r="R28" t="n">
-        <v>6521987</v>
+        <v>6522087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3666,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122467685</v>
+        <v>122471527</v>
       </c>
       <c r="B29" t="n">
-        <v>56589</v>
+        <v>80609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,46 +3678,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565996</v>
+        <v>566071</v>
       </c>
       <c r="R29" t="n">
-        <v>6522087</v>
+        <v>6522065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3770,6 +3748,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3788,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122471527</v>
+        <v>122466836</v>
       </c>
       <c r="B30" t="n">
-        <v>80608</v>
+        <v>79270</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3804,40 +3783,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566071</v>
+        <v>566112</v>
       </c>
       <c r="R30" t="n">
-        <v>6522065</v>
+        <v>6521987</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3875,7 +3846,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3894,10 +3864,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467759</v>
+        <v>122467142</v>
       </c>
       <c r="B31" t="n">
-        <v>90773</v>
+        <v>92087</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,21 +3880,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3934,10 +3899,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565945</v>
+        <v>566070</v>
       </c>
       <c r="R31" t="n">
-        <v>6522131</v>
+        <v>6522054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122467101</v>
+        <v>122466836</v>
       </c>
       <c r="B25" t="n">
-        <v>79270</v>
+        <v>79274</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3291,6 +3291,11 @@
       <c r="E25" t="n">
         <v>6453</v>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Hertelidea botryosa</t>
@@ -3308,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566070</v>
+        <v>566112</v>
       </c>
       <c r="R25" t="n">
-        <v>6522077</v>
+        <v>6521987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3370,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122466971</v>
+        <v>122467685</v>
       </c>
       <c r="B26" t="n">
-        <v>79270</v>
+        <v>56593</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3382,33 +3387,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566063</v>
+        <v>565996</v>
       </c>
       <c r="R26" t="n">
-        <v>6522107</v>
+        <v>6522087</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3467,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467759</v>
+        <v>122466971</v>
       </c>
       <c r="B27" t="n">
-        <v>90778</v>
+        <v>79274</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3479,20 +3494,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3502,10 +3522,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565945</v>
+        <v>566063</v>
       </c>
       <c r="R27" t="n">
-        <v>6522131</v>
+        <v>6522107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,10 +3584,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467685</v>
+        <v>122467101</v>
       </c>
       <c r="B28" t="n">
-        <v>56589</v>
+        <v>79274</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3576,38 +3596,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565996</v>
+        <v>566070</v>
       </c>
       <c r="R28" t="n">
-        <v>6522087</v>
+        <v>6522077</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3666,10 +3686,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122471527</v>
+        <v>122467759</v>
       </c>
       <c r="B29" t="n">
-        <v>80609</v>
+        <v>90791</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3678,39 +3698,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566071</v>
+        <v>565945</v>
       </c>
       <c r="R29" t="n">
-        <v>6522065</v>
+        <v>6522131</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3748,7 +3770,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3767,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122466836</v>
+        <v>122471527</v>
       </c>
       <c r="B30" t="n">
-        <v>79270</v>
+        <v>80613</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,32 +3804,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>1049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566112</v>
+        <v>566071</v>
       </c>
       <c r="R30" t="n">
-        <v>6521987</v>
+        <v>6522065</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3846,6 +3875,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3867,7 +3897,7 @@
         <v>122467142</v>
       </c>
       <c r="B31" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3881,6 +3911,11 @@
       </c>
       <c r="E31" t="n">
         <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122467685</v>
+        <v>122467759</v>
       </c>
       <c r="B26" t="n">
-        <v>56593</v>
+        <v>90804</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,39 +3391,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565996</v>
+        <v>565945</v>
       </c>
       <c r="R26" t="n">
-        <v>6522087</v>
+        <v>6522131</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,10 +3477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122466971</v>
+        <v>122467685</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>56593</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,38 +3489,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566063</v>
+        <v>565996</v>
       </c>
       <c r="R27" t="n">
-        <v>6522107</v>
+        <v>6522087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122467759</v>
+        <v>122466971</v>
       </c>
       <c r="B29" t="n">
-        <v>90791</v>
+        <v>79274</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3698,25 +3698,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565945</v>
+        <v>566063</v>
       </c>
       <c r="R29" t="n">
-        <v>6522131</v>
+        <v>6522107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3897,7 +3897,7 @@
         <v>122467142</v>
       </c>
       <c r="B31" t="n">
-        <v>92100</v>
+        <v>92113</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122466836</v>
+        <v>122467142</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>92113</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,25 +3285,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566112</v>
+        <v>566070</v>
       </c>
       <c r="R25" t="n">
-        <v>6521987</v>
+        <v>6522054</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122467759</v>
+        <v>122466836</v>
       </c>
       <c r="B26" t="n">
-        <v>90804</v>
+        <v>79274</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,25 +3387,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565945</v>
+        <v>566112</v>
       </c>
       <c r="R26" t="n">
-        <v>6522131</v>
+        <v>6521987</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467685</v>
+        <v>122467101</v>
       </c>
       <c r="B27" t="n">
-        <v>56593</v>
+        <v>79274</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3489,43 +3489,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565996</v>
+        <v>566070</v>
       </c>
       <c r="R27" t="n">
-        <v>6522087</v>
+        <v>6522077</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3584,10 +3579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467101</v>
+        <v>122467759</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>90804</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3596,25 +3591,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3624,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R28" t="n">
-        <v>6522077</v>
+        <v>6522131</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122466971</v>
+        <v>122471527</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>80613</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3702,37 +3697,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566063</v>
+        <v>566071</v>
       </c>
       <c r="R29" t="n">
-        <v>6522107</v>
+        <v>6522065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3770,6 +3768,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3788,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122471527</v>
+        <v>122466971</v>
       </c>
       <c r="B30" t="n">
-        <v>80613</v>
+        <v>79274</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3804,40 +3803,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566071</v>
+        <v>566063</v>
       </c>
       <c r="R30" t="n">
-        <v>6522065</v>
+        <v>6522107</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3875,7 +3871,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3894,10 +3889,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467142</v>
+        <v>122467685</v>
       </c>
       <c r="B31" t="n">
-        <v>92113</v>
+        <v>56593</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,34 +3905,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566070</v>
+        <v>565996</v>
       </c>
       <c r="R31" t="n">
-        <v>6522054</v>
+        <v>6522087</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122467142</v>
+        <v>122467759</v>
       </c>
       <c r="B25" t="n">
-        <v>92113</v>
+        <v>90798</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R25" t="n">
-        <v>6522054</v>
+        <v>6522131</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467101</v>
+        <v>122466971</v>
       </c>
       <c r="B27" t="n">
         <v>79274</v>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566070</v>
+        <v>566063</v>
       </c>
       <c r="R27" t="n">
-        <v>6522077</v>
+        <v>6522107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3579,10 +3579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467759</v>
+        <v>122471527</v>
       </c>
       <c r="B28" t="n">
-        <v>90804</v>
+        <v>80613</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,41 +3591,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565945</v>
+        <v>566071</v>
       </c>
       <c r="R28" t="n">
-        <v>6522131</v>
+        <v>6522065</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3663,6 +3666,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3681,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122471527</v>
+        <v>122467685</v>
       </c>
       <c r="B29" t="n">
-        <v>80613</v>
+        <v>56593</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,44 +3697,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566071</v>
+        <v>565996</v>
       </c>
       <c r="R29" t="n">
-        <v>6522065</v>
+        <v>6522087</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3768,7 +3774,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3787,7 +3792,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122466971</v>
+        <v>122467101</v>
       </c>
       <c r="B30" t="n">
         <v>79274</v>
@@ -3827,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566063</v>
+        <v>566070</v>
       </c>
       <c r="R30" t="n">
-        <v>6522107</v>
+        <v>6522077</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3889,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467685</v>
+        <v>122467142</v>
       </c>
       <c r="B31" t="n">
-        <v>56593</v>
+        <v>92114</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3905,39 +3910,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565996</v>
+        <v>566070</v>
       </c>
       <c r="R31" t="n">
-        <v>6522087</v>
+        <v>6522054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122467759</v>
+        <v>122466971</v>
       </c>
       <c r="B25" t="n">
-        <v>90798</v>
+        <v>79274</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,25 +3285,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565945</v>
+        <v>566063</v>
       </c>
       <c r="R25" t="n">
-        <v>6522131</v>
+        <v>6522107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122466971</v>
+        <v>122471527</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>80613</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3493,37 +3493,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566063</v>
+        <v>566071</v>
       </c>
       <c r="R27" t="n">
-        <v>6522107</v>
+        <v>6522065</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,6 +3564,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3579,10 +3583,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122471527</v>
+        <v>122467101</v>
       </c>
       <c r="B28" t="n">
-        <v>80613</v>
+        <v>79274</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,40 +3599,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566071</v>
+        <v>566070</v>
       </c>
       <c r="R28" t="n">
-        <v>6522065</v>
+        <v>6522077</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3666,7 +3667,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122467101</v>
+        <v>122467142</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>92114</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3804,25 +3804,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3835,7 +3835,7 @@
         <v>566070</v>
       </c>
       <c r="R30" t="n">
-        <v>6522077</v>
+        <v>6522054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467142</v>
+        <v>122467759</v>
       </c>
       <c r="B31" t="n">
-        <v>92114</v>
+        <v>90798</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R31" t="n">
-        <v>6522054</v>
+        <v>6522131</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122466971</v>
+        <v>122466836</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566063</v>
+        <v>566112</v>
       </c>
       <c r="R25" t="n">
-        <v>6522107</v>
+        <v>6521987</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122466836</v>
+        <v>122467685</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>56594</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,38 +3387,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566112</v>
+        <v>565996</v>
       </c>
       <c r="R26" t="n">
-        <v>6521987</v>
+        <v>6522087</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,7 +3485,7 @@
         <v>122471527</v>
       </c>
       <c r="B27" t="n">
-        <v>80613</v>
+        <v>80614</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,10 +3588,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467101</v>
+        <v>122466971</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>79275</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,10 +3628,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566070</v>
+        <v>566063</v>
       </c>
       <c r="R28" t="n">
-        <v>6522077</v>
+        <v>6522107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3685,10 +3690,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122467685</v>
+        <v>122467101</v>
       </c>
       <c r="B29" t="n">
-        <v>56593</v>
+        <v>79275</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3697,43 +3702,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565996</v>
+        <v>566070</v>
       </c>
       <c r="R29" t="n">
-        <v>6522087</v>
+        <v>6522077</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122467142</v>
+        <v>122467759</v>
       </c>
       <c r="B30" t="n">
-        <v>92114</v>
+        <v>90799</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R30" t="n">
-        <v>6522054</v>
+        <v>6522131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467759</v>
+        <v>122467142</v>
       </c>
       <c r="B31" t="n">
-        <v>90798</v>
+        <v>92115</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565945</v>
+        <v>566070</v>
       </c>
       <c r="R31" t="n">
-        <v>6522131</v>
+        <v>6522054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122466836</v>
+        <v>122466971</v>
       </c>
       <c r="B25" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566112</v>
+        <v>566063</v>
       </c>
       <c r="R25" t="n">
-        <v>6521987</v>
+        <v>6522107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122467685</v>
+        <v>122471527</v>
       </c>
       <c r="B26" t="n">
-        <v>56594</v>
+        <v>80617</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,46 +3387,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565996</v>
+        <v>566071</v>
       </c>
       <c r="R26" t="n">
-        <v>6522087</v>
+        <v>6522065</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3464,6 +3462,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3482,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122471527</v>
+        <v>122467101</v>
       </c>
       <c r="B27" t="n">
-        <v>80614</v>
+        <v>79278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3498,40 +3497,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566071</v>
+        <v>566070</v>
       </c>
       <c r="R27" t="n">
-        <v>6522065</v>
+        <v>6522077</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3569,7 +3565,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3588,10 +3583,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122466971</v>
+        <v>122467142</v>
       </c>
       <c r="B28" t="n">
-        <v>79275</v>
+        <v>92118</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3600,25 +3595,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3628,10 +3623,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566063</v>
+        <v>566070</v>
       </c>
       <c r="R28" t="n">
-        <v>6522107</v>
+        <v>6522054</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3690,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122467101</v>
+        <v>122466836</v>
       </c>
       <c r="B29" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566070</v>
+        <v>566112</v>
       </c>
       <c r="R29" t="n">
-        <v>6522077</v>
+        <v>6521987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122467759</v>
+        <v>122467685</v>
       </c>
       <c r="B30" t="n">
-        <v>90799</v>
+        <v>56594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3808,34 +3803,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565945</v>
+        <v>565996</v>
       </c>
       <c r="R30" t="n">
-        <v>6522131</v>
+        <v>6522087</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467142</v>
+        <v>122467759</v>
       </c>
       <c r="B31" t="n">
-        <v>92115</v>
+        <v>90802</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R31" t="n">
-        <v>6522054</v>
+        <v>6522131</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,7 +3273,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122466971</v>
+        <v>122467101</v>
       </c>
       <c r="B25" t="n">
         <v>79278</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566063</v>
+        <v>566070</v>
       </c>
       <c r="R25" t="n">
-        <v>6522107</v>
+        <v>6522077</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122471527</v>
+        <v>122467142</v>
       </c>
       <c r="B26" t="n">
-        <v>80617</v>
+        <v>92118</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,44 +3387,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566071</v>
+        <v>566070</v>
       </c>
       <c r="R26" t="n">
-        <v>6522065</v>
+        <v>6522054</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3462,7 +3459,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3481,10 +3477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467101</v>
+        <v>122467759</v>
       </c>
       <c r="B27" t="n">
-        <v>79278</v>
+        <v>90802</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3493,25 +3489,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3521,10 +3517,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R27" t="n">
-        <v>6522077</v>
+        <v>6522131</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3583,10 +3579,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467142</v>
+        <v>122467685</v>
       </c>
       <c r="B28" t="n">
-        <v>92118</v>
+        <v>56594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,34 +3595,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566070</v>
+        <v>565996</v>
       </c>
       <c r="R28" t="n">
-        <v>6522054</v>
+        <v>6522087</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3685,7 +3686,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122466836</v>
+        <v>122466971</v>
       </c>
       <c r="B29" t="n">
         <v>79278</v>
@@ -3725,10 +3726,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566112</v>
+        <v>566063</v>
       </c>
       <c r="R29" t="n">
-        <v>6521987</v>
+        <v>6522107</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122467685</v>
+        <v>122466836</v>
       </c>
       <c r="B30" t="n">
-        <v>56594</v>
+        <v>79278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3799,43 +3800,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565996</v>
+        <v>566112</v>
       </c>
       <c r="R30" t="n">
-        <v>6522087</v>
+        <v>6521987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3890,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467759</v>
+        <v>122471527</v>
       </c>
       <c r="B31" t="n">
-        <v>90802</v>
+        <v>80617</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3906,41 +3902,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565945</v>
+        <v>566071</v>
       </c>
       <c r="R31" t="n">
-        <v>6522131</v>
+        <v>6522065</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3978,6 +3977,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122467101</v>
+        <v>122467142</v>
       </c>
       <c r="B25" t="n">
-        <v>79278</v>
+        <v>92221</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,25 +3285,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,7 +3316,7 @@
         <v>566070</v>
       </c>
       <c r="R25" t="n">
-        <v>6522077</v>
+        <v>6522054</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122467142</v>
+        <v>122466971</v>
       </c>
       <c r="B26" t="n">
-        <v>92118</v>
+        <v>79380</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,25 +3387,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566070</v>
+        <v>566063</v>
       </c>
       <c r="R26" t="n">
-        <v>6522054</v>
+        <v>6522107</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467759</v>
+        <v>122467685</v>
       </c>
       <c r="B27" t="n">
-        <v>90802</v>
+        <v>56688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3493,34 +3493,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565945</v>
+        <v>565996</v>
       </c>
       <c r="R27" t="n">
-        <v>6522131</v>
+        <v>6522087</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3579,10 +3584,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467685</v>
+        <v>122471527</v>
       </c>
       <c r="B28" t="n">
-        <v>56594</v>
+        <v>80719</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,46 +3596,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565996</v>
+        <v>566071</v>
       </c>
       <c r="R28" t="n">
-        <v>6522087</v>
+        <v>6522065</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3668,6 +3671,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3686,10 +3690,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122466971</v>
+        <v>122467101</v>
       </c>
       <c r="B29" t="n">
-        <v>79278</v>
+        <v>79380</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3726,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566063</v>
+        <v>566070</v>
       </c>
       <c r="R29" t="n">
-        <v>6522107</v>
+        <v>6522077</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3788,10 +3792,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122466836</v>
+        <v>122467759</v>
       </c>
       <c r="B30" t="n">
-        <v>79278</v>
+        <v>90905</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3800,25 +3804,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3828,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566112</v>
+        <v>565945</v>
       </c>
       <c r="R30" t="n">
-        <v>6521987</v>
+        <v>6522131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3890,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122471527</v>
+        <v>122466836</v>
       </c>
       <c r="B31" t="n">
-        <v>80617</v>
+        <v>79380</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3906,40 +3910,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566071</v>
+        <v>566112</v>
       </c>
       <c r="R31" t="n">
-        <v>6522065</v>
+        <v>6521987</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3977,7 +3978,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122467142</v>
+        <v>122471527</v>
       </c>
       <c r="B25" t="n">
-        <v>92221</v>
+        <v>80723</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,41 +3285,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566070</v>
+        <v>566071</v>
       </c>
       <c r="R25" t="n">
-        <v>6522054</v>
+        <v>6522065</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3357,6 +3360,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3375,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122466971</v>
+        <v>122467101</v>
       </c>
       <c r="B26" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3415,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566063</v>
+        <v>566070</v>
       </c>
       <c r="R26" t="n">
-        <v>6522107</v>
+        <v>6522077</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467685</v>
+        <v>122466836</v>
       </c>
       <c r="B27" t="n">
-        <v>56688</v>
+        <v>79384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3489,43 +3493,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565996</v>
+        <v>566112</v>
       </c>
       <c r="R27" t="n">
-        <v>6522087</v>
+        <v>6521987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3584,10 +3583,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122471527</v>
+        <v>122467759</v>
       </c>
       <c r="B28" t="n">
-        <v>80719</v>
+        <v>90909</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3596,44 +3595,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566071</v>
+        <v>565945</v>
       </c>
       <c r="R28" t="n">
-        <v>6522065</v>
+        <v>6522131</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3671,7 +3667,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3690,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122467101</v>
+        <v>122467685</v>
       </c>
       <c r="B29" t="n">
-        <v>79380</v>
+        <v>56688</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3702,38 +3697,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566070</v>
+        <v>565996</v>
       </c>
       <c r="R29" t="n">
-        <v>6522077</v>
+        <v>6522087</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122467759</v>
+        <v>122467142</v>
       </c>
       <c r="B30" t="n">
-        <v>90905</v>
+        <v>92225</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565945</v>
+        <v>566070</v>
       </c>
       <c r="R30" t="n">
-        <v>6522131</v>
+        <v>6522054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122466836</v>
+        <v>122466971</v>
       </c>
       <c r="B31" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566112</v>
+        <v>566063</v>
       </c>
       <c r="R31" t="n">
-        <v>6521987</v>
+        <v>6522107</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122471527</v>
+        <v>122467685</v>
       </c>
       <c r="B25" t="n">
-        <v>80723</v>
+        <v>56688</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,44 +3285,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566071</v>
+        <v>565996</v>
       </c>
       <c r="R25" t="n">
-        <v>6522065</v>
+        <v>6522087</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3360,7 +3362,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3379,10 +3380,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122467101</v>
+        <v>122467759</v>
       </c>
       <c r="B26" t="n">
-        <v>79384</v>
+        <v>90909</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,25 +3392,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3419,10 +3420,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566070</v>
+        <v>565945</v>
       </c>
       <c r="R26" t="n">
-        <v>6522077</v>
+        <v>6522131</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3481,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122466836</v>
+        <v>122467101</v>
       </c>
       <c r="B27" t="n">
         <v>79384</v>
@@ -3521,10 +3522,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566112</v>
+        <v>566070</v>
       </c>
       <c r="R27" t="n">
-        <v>6521987</v>
+        <v>6522077</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3583,10 +3584,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122467759</v>
+        <v>122466971</v>
       </c>
       <c r="B28" t="n">
-        <v>90909</v>
+        <v>79384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3595,25 +3596,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3623,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565945</v>
+        <v>566063</v>
       </c>
       <c r="R28" t="n">
-        <v>6522131</v>
+        <v>6522107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3685,10 +3686,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122467685</v>
+        <v>122471527</v>
       </c>
       <c r="B29" t="n">
-        <v>56688</v>
+        <v>80723</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3697,46 +3698,44 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565996</v>
+        <v>566071</v>
       </c>
       <c r="R29" t="n">
-        <v>6522087</v>
+        <v>6522065</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3774,6 +3773,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122467142</v>
+        <v>122466836</v>
       </c>
       <c r="B30" t="n">
-        <v>92225</v>
+        <v>79384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3804,25 +3804,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566070</v>
+        <v>566112</v>
       </c>
       <c r="R30" t="n">
-        <v>6522054</v>
+        <v>6521987</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122466971</v>
+        <v>122467142</v>
       </c>
       <c r="B31" t="n">
-        <v>79384</v>
+        <v>92225</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3906,25 +3906,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566063</v>
+        <v>566070</v>
       </c>
       <c r="R31" t="n">
-        <v>6522107</v>
+        <v>6522054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122467685</v>
+        <v>122466971</v>
       </c>
       <c r="B25" t="n">
-        <v>56688</v>
+        <v>79384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,43 +3285,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565996</v>
+        <v>566063</v>
       </c>
       <c r="R25" t="n">
-        <v>6522087</v>
+        <v>6522107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3380,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122467759</v>
+        <v>122471527</v>
       </c>
       <c r="B26" t="n">
-        <v>90909</v>
+        <v>80723</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,41 +3387,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565945</v>
+        <v>566071</v>
       </c>
       <c r="R26" t="n">
-        <v>6522131</v>
+        <v>6522065</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3464,6 +3462,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3482,7 +3481,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122467101</v>
+        <v>122466836</v>
       </c>
       <c r="B27" t="n">
         <v>79384</v>
@@ -3522,10 +3521,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566070</v>
+        <v>566112</v>
       </c>
       <c r="R27" t="n">
-        <v>6522077</v>
+        <v>6521987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3584,7 +3583,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122466971</v>
+        <v>122467101</v>
       </c>
       <c r="B28" t="n">
         <v>79384</v>
@@ -3624,10 +3623,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566063</v>
+        <v>566070</v>
       </c>
       <c r="R28" t="n">
-        <v>6522107</v>
+        <v>6522077</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122471527</v>
+        <v>122467759</v>
       </c>
       <c r="B29" t="n">
-        <v>80723</v>
+        <v>90909</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3698,44 +3697,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566071</v>
+        <v>565945</v>
       </c>
       <c r="R29" t="n">
-        <v>6522065</v>
+        <v>6522131</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3773,7 +3769,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3792,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122466836</v>
+        <v>122467142</v>
       </c>
       <c r="B30" t="n">
-        <v>79384</v>
+        <v>92225</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3804,25 +3799,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3832,10 +3827,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566112</v>
+        <v>566070</v>
       </c>
       <c r="R30" t="n">
-        <v>6521987</v>
+        <v>6522054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3889,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122467142</v>
+        <v>122467685</v>
       </c>
       <c r="B31" t="n">
-        <v>92225</v>
+        <v>56688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3910,34 +3905,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skräpdalen, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566070</v>
+        <v>565996</v>
       </c>
       <c r="R31" t="n">
-        <v>6522054</v>
+        <v>6522087</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3892,7 +3892,7 @@
         <v>122467685</v>
       </c>
       <c r="B31" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 651-2025 artfynd.xlsx
+++ b/artfynd/A 651-2025 artfynd.xlsx
@@ -3892,7 +3892,7 @@
         <v>122467685</v>
       </c>
       <c r="B31" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
